--- a/tests/fixtures/spreadsheet/sample_data.xlsx
+++ b/tests/fixtures/spreadsheet/sample_data.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,171 +413,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Age</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Alice</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Yaoundé</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>95.5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Bob</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Douala</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>88.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>35</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Limbe</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>92.09999999999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Diana</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Buea</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>85.7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>City</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Widget A</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="C2" t="n">
-        <v>100</v>
+        <v>30</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gadget B</t>
+          <t>Bob</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49.99</v>
-      </c>
-      <c r="C3" t="n">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tool C</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="C4" t="n">
-        <v>200</v>
+        <v>35</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
       </c>
     </row>
   </sheetData>
